--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981ABF7A-6368-4D8A-8B73-E1F1F2F0946F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3FB40E74962C70D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097215C2-36E0-4DFA-AA4C-3E097CBEF27D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 09-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 14-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3FB40E74962C70D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097215C2-36E0-4DFA-AA4C-3E097CBEF27D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F145EF19F0C71D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3718C6B0-8B40-416E-8C09-7A0C4A881B25}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F145EF19F0C71D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3718C6B0-8B40-416E-8C09-7A0C4A881B25}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06F89FF-F834-4B4C-B84B-EDB9418DB2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06F89FF-F834-4B4C-B84B-EDB9418DB2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FAC92A-42D3-4843-91F6-1C6561B072DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 14-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 17-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FAC92A-42D3-4843-91F6-1C6561B072DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44F584A-4222-43A5-A65E-53B191D75852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44F584A-4222-43A5-A65E-53B191D75852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3FE406339E0671D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B73B89-3F71-4231-A506-C5AEB00B0E4C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 17-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 18-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3FE406339E0671D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B73B89-3F71-4231-A506-C5AEB00B0E4C}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F769631860E71D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3EB8353-F831-4520-BF77-9AE73A041072}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 18-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 21-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F769631860E71D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3EB8353-F831-4520-BF77-9AE73A041072}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899EF250-8687-4A38-BD53-1DF8C0D86F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899EF250-8687-4A38-BD53-1DF8C0D86F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5543EE-4A7E-43BC-89F2-47436031D4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 21-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 22-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5543EE-4A7E-43BC-89F2-47436031D4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BFC7C6-9295-4B71-901A-874501D7552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BFC7C6-9295-4B71-901A-874501D7552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C338142-4229-4FCB-AE3D-1B3070F48E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 22-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 23-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C338142-4229-4FCB-AE3D-1B3070F48E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F974E729E8871D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFC734CE-1A27-459C-B5F1-2216DA388ECA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F974E729E8871D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFC734CE-1A27-459C-B5F1-2216DA388ECA}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3FD3EE3499B870D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFFF61DC-491F-401B-9E69-352283B1FB00}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 23-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 24-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3FD3EE3499B870D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFFF61DC-491F-401B-9E69-352283B1FB00}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F21B63290C670D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CCCDCC7-21FC-4F82-B006-3A7F8BE63CBD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F21B63290C670D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CCCDCC7-21FC-4F82-B006-3A7F8BE63CBD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51718887-364E-4DF9-A6F6-AF5162971CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 24-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 28-09-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51718887-364E-4DF9-A6F6-AF5162971CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3FC47E779BE670D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{748FC88E-320F-4A4F-8D6B-E13E9705AF8A}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 28-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 02-10-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BFC7C6-9295-4B71-901A-874501D7552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0AAC87-0BBD-43FE-B8A1-FB9FF91D1459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 22-09-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 07-10-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3FC47E779BE670D84809" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{748FC88E-320F-4A4F-8D6B-E13E9705AF8A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A5F5A1-F12C-4518-A51C-2F0085C8FAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 02-10-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 07-10-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -725,7 +725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -745,7 +745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -810,7 +810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -855,7 +855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -869,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -966,7 +966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>30</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>87</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A5F5A1-F12C-4518-A51C-2F0085C8FAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F6506778C5070D84815" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8DE0CD8-EC30-462E-938D-847F096562C4}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 07-10-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 08-10-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DA9533E3D7EB3F6506778C5070D84815" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8DE0CD8-EC30-462E-938D-847F096562C4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17CBB00-442E-4359-B9AB-99B77B8C32EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 08-10-2026'!$A$1:$I$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 09-10-2026'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/EOJ-Systemer_excel.XLSX
+++ b/html/EOJ-Systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BE7881-1309-4BF1-940D-6FA7F90575DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9CC253D85B1892CE57E759C4071D84843" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C465D27C-CE31-49D2-9C27-8D13A9F4E432}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="EOJ_Systemer">'Opdateret d. 09-10-2026'!$A$1:$J$65</definedName>
+    <definedName name="EOJ_Systemer">'Opdateret d. 23-10-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
